--- a/artfynd/A 33273-2021 artfynd.xlsx
+++ b/artfynd/A 33273-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33273-2021 artfynd.xlsx
+++ b/artfynd/A 33273-2021 artfynd.xlsx
@@ -917,12 +917,7 @@
         <v>84450651</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -954,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>284203.2255937392</v>
+        <v>284203</v>
       </c>
       <c r="R4" t="n">
-        <v>6555165.249617893</v>
+        <v>6555165</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -987,19 +982,9 @@
           <t>1996-07-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1996-07-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 33273-2021 artfynd.xlsx
+++ b/artfynd/A 33273-2021 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>84450651</v>
       </c>
       <c r="B4" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33273-2021 artfynd.xlsx
+++ b/artfynd/A 33273-2021 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>84450651</v>
       </c>
       <c r="B4" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33273-2021 artfynd.xlsx
+++ b/artfynd/A 33273-2021 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>84450651</v>
       </c>
       <c r="B4" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33273-2021 artfynd.xlsx
+++ b/artfynd/A 33273-2021 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>84450651</v>
       </c>
       <c r="B4" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33273-2021 artfynd.xlsx
+++ b/artfynd/A 33273-2021 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>84450651</v>
       </c>
       <c r="B4" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33273-2021 artfynd.xlsx
+++ b/artfynd/A 33273-2021 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>84450651</v>
       </c>
       <c r="B4" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33273-2021 artfynd.xlsx
+++ b/artfynd/A 33273-2021 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>84450651</v>
       </c>
       <c r="B4" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33273-2021 artfynd.xlsx
+++ b/artfynd/A 33273-2021 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>84450651</v>
       </c>
       <c r="B4" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33273-2021 artfynd.xlsx
+++ b/artfynd/A 33273-2021 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>84450651</v>
       </c>
       <c r="B4" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33273-2021 artfynd.xlsx
+++ b/artfynd/A 33273-2021 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>84450651</v>
       </c>
       <c r="B4" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
